--- a/Team-Data/2008-09/3-20-2008-09.xlsx
+++ b/Team-Data/2008-09/3-20-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -790,7 +857,7 @@
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -861,67 +928,67 @@
         <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,13 +1000,13 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -951,22 +1018,22 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -975,22 +1042,22 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1025,31 +1092,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.449</v>
+        <v>0.441</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J4" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>16.2</v>
@@ -1058,22 +1125,22 @@
         <v>0.374</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
@@ -1088,43 +1155,43 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
         <v>21.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>5</v>
       </c>
       <c r="AI4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
@@ -1160,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.456</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.452</v>
@@ -1240,19 +1307,19 @@
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
         <v>42.6</v>
@@ -1261,7 +1328,7 @@
         <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1276,16 +1343,16 @@
         <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>23</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1330,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,7 +1406,7 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1354,7 +1421,7 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
         <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.821</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
@@ -1437,37 +1504,37 @@
         <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1497,13 +1564,13 @@
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>24</v>
@@ -1512,7 +1579,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>14</v>
@@ -1524,19 +1591,19 @@
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
         <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1595,10 +1662,10 @@
         <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
         <v>0.345</v>
@@ -1610,22 +1677,22 @@
         <v>22.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
         <v>42.9</v>
       </c>
       <c r="U7" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W7" t="n">
         <v>7.3</v>
@@ -1643,13 +1710,13 @@
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC7" t="n">
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1679,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1691,13 +1758,13 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
@@ -1706,7 +1773,7 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1715,7 +1782,7 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.643</v>
+        <v>0.638</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J8" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.758</v>
       </c>
       <c r="R8" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
         <v>41.7</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V8" t="n">
         <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
@@ -1822,19 +1889,19 @@
         <v>22.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD8" t="n">
         <v>3</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1864,7 +1931,7 @@
         <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
@@ -1876,34 +1943,34 @@
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>25</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>26</v>
-      </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J9" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,31 +2032,31 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O9" t="n">
         <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.751</v>
       </c>
       <c r="R9" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S9" t="n">
         <v>29.8</v>
       </c>
       <c r="T9" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W9" t="n">
         <v>6.3</v>
@@ -2001,22 +2068,22 @@
         <v>4.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
@@ -2028,10 +2095,10 @@
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2061,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J10" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O10" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="P10" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0.786</v>
       </c>
       <c r="R10" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S10" t="n">
         <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2225,10 +2292,10 @@
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
@@ -2237,13 +2304,13 @@
         <v>10</v>
       </c>
       <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT10" t="n">
         <v>10</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>14</v>
@@ -2252,7 +2319,7 @@
         <v>23</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2261,10 +2328,10 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.648</v>
+        <v>0.643</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L11" t="n">
         <v>7.6</v>
@@ -2329,16 +2396,16 @@
         <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P11" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
@@ -2368,13 +2435,13 @@
         <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2398,7 +2465,7 @@
         <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,22 +2474,22 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2440,7 +2507,7 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2449,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,7 +2566,7 @@
         <v>38.7</v>
       </c>
       <c r="J12" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.449</v>
@@ -2508,19 +2575,19 @@
         <v>7.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O12" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
@@ -2532,13 +2599,13 @@
         <v>43.5</v>
       </c>
       <c r="U12" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.2</v>
@@ -2553,13 +2620,13 @@
         <v>21.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.8</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2595,10 +2662,10 @@
         <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>12</v>
@@ -2610,22 +2677,22 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA12" t="n">
         <v>13</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
         <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,46 +2748,46 @@
         <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R13" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>5.9</v>
@@ -2729,19 +2796,19 @@
         <v>5.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB13" t="n">
         <v>95.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2777,7 +2844,7 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
@@ -2786,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
@@ -2798,16 +2865,16 @@
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,58 +2939,58 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O14" t="n">
         <v>19.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
         <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2953,22 +3020,22 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2980,16 +3047,16 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
         <v>7</v>
       </c>
       <c r="AY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3094,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>77.5</v>
+        <v>77.7</v>
       </c>
       <c r="K15" t="n">
         <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N15" t="n">
         <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S15" t="n">
         <v>28.4</v>
@@ -3081,31 +3148,31 @@
         <v>17.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA15" t="n">
         <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>13</v>
       </c>
       <c r="AI15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ15" t="n">
         <v>27</v>
@@ -3135,16 +3202,16 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
         <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>0.529</v>
+        <v>0.537</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3230,7 +3297,7 @@
         <v>81.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -3239,16 +3306,16 @@
         <v>19.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
         <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
@@ -3260,19 +3327,19 @@
         <v>39.3</v>
       </c>
       <c r="U16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
         <v>12.6</v>
       </c>
       <c r="W16" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X16" t="n">
         <v>5.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
         <v>20.7</v>
@@ -3281,19 +3348,19 @@
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
@@ -3317,13 +3384,13 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3338,19 +3405,19 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3359,7 +3426,7 @@
         <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>0.449</v>
+        <v>0.443</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,22 +3479,22 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.784</v>
@@ -3436,16 +3503,16 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.3</v>
@@ -3457,34 +3524,34 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3514,25 +3581,25 @@
         <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.29</v>
+        <v>0.294</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3597,34 +3664,34 @@
         <v>0.442</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
         <v>24.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
         <v>29.9</v>
       </c>
       <c r="T18" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
         <v>14.3</v>
@@ -3639,19 +3706,19 @@
         <v>6.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.6</v>
+        <v>-4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3678,19 +3745,19 @@
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
         <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3699,13 +3766,13 @@
         <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3720,10 +3787,10 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.435</v>
+        <v>0.426</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3773,7 +3840,7 @@
         <v>36</v>
       </c>
       <c r="J19" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.45</v>
@@ -3785,10 +3852,10 @@
         <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="O19" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
         <v>24.3</v>
@@ -3800,13 +3867,13 @@
         <v>10.4</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T19" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V19" t="n">
         <v>13.2</v>
@@ -3815,7 +3882,7 @@
         <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
         <v>4.8</v>
@@ -3827,19 +3894,19 @@
         <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
         <v>22</v>
@@ -3863,7 +3930,7 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3884,31 +3951,31 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.632</v>
+        <v>0.627</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3955,31 +4022,31 @@
         <v>35.2</v>
       </c>
       <c r="J20" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K20" t="n">
         <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M20" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
         <v>18.4</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
         <v>29.9</v>
@@ -4012,13 +4079,13 @@
         <v>95.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
@@ -4033,10 +4100,10 @@
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>10</v>
@@ -4045,19 +4112,19 @@
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
         <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
@@ -4072,10 +4139,10 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
         <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>0.412</v>
+        <v>0.418</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
         <v>86.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
         <v>10.3</v>
       </c>
       <c r="M21" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O21" t="n">
         <v>18.4</v>
@@ -4164,25 +4231,25 @@
         <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>7.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z21" t="n">
         <v>20.5</v>
@@ -4191,25 +4258,25 @@
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.6</v>
+        <v>105.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4221,7 +4288,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4254,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
         <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.275</v>
+        <v>0.279</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
         <v>81.8</v>
@@ -4328,49 +4395,49 @@
         <v>4.1</v>
       </c>
       <c r="M22" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="P22" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.787</v>
       </c>
       <c r="R22" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S22" t="n">
         <v>30.4</v>
       </c>
       <c r="T22" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V22" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
         <v>4.9</v>
       </c>
       <c r="Z22" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AA22" t="n">
         <v>20.6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>20.5</v>
       </c>
       <c r="AB22" t="n">
         <v>97.5</v>
@@ -4379,7 +4446,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,7 +4458,7 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>16</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4424,10 +4491,10 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>24</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,10 +4512,10 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4585,16 +4652,16 @@
         <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4615,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
         <v>34</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,49 +4750,49 @@
         <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>80.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O24" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="P24" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="R24" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="S24" t="n">
         <v>29.2</v>
       </c>
       <c r="T24" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y24" t="n">
         <v>4.8</v>
@@ -4734,16 +4801,16 @@
         <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4761,10 +4828,10 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,31 +4843,31 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS24" t="n">
         <v>22</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -4812,10 +4879,10 @@
         <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4964,22 +5031,22 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW25" t="n">
         <v>24</v>
@@ -4994,7 +5061,7 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>2</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" t="n">
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.632</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
         <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R26" t="n">
         <v>12.8</v>
@@ -5077,10 +5144,10 @@
         <v>28.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5095,37 +5162,37 @@
         <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5137,19 +5204,19 @@
         <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS26" t="n">
         <v>28</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA26" t="n">
         <v>12</v>
       </c>
-      <c r="BA26" t="n">
-        <v>11</v>
-      </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" t="n">
         <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>0.217</v>
+        <v>0.206</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
@@ -5250,16 +5317,16 @@
         <v>25.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.804</v>
+        <v>0.803</v>
       </c>
       <c r="R27" t="n">
         <v>10</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="U27" t="n">
         <v>19.7</v>
@@ -5283,19 +5350,19 @@
         <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.4</v>
+        <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5304,7 +5371,7 @@
         <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -5319,22 +5386,22 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS27" t="n">
         <v>27</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>26</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5343,7 +5410,7 @@
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5355,10 +5422,10 @@
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5460,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
         <v>45</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>0.662</v>
+        <v>0.672</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
         <v>79.7</v>
@@ -5417,43 +5484,43 @@
         <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M28" t="n">
         <v>19.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.392</v>
+        <v>0.394</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P28" t="n">
         <v>19.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T28" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V28" t="n">
         <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
@@ -5465,16 +5532,16 @@
         <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,19 +5577,19 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G29" t="n">
-        <v>0.348</v>
+        <v>0.353</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K29" t="n">
         <v>0.456</v>
@@ -5602,37 +5669,37 @@
         <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P29" t="n">
         <v>22.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T29" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W29" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X29" t="n">
         <v>4.7</v>
@@ -5641,34 +5708,34 @@
         <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA29" t="n">
         <v>20.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>19</v>
@@ -5683,10 +5750,10 @@
         <v>23</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
         <v>25</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
         <v>26</v>
@@ -5713,13 +5780,13 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
         <v>0.477</v>
       </c>
       <c r="L30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
         <v>27.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R30" t="n">
         <v>11.7</v>
@@ -5811,10 +5878,10 @@
         <v>24.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
         <v>4.7</v>
@@ -5823,7 +5890,7 @@
         <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA30" t="n">
         <v>23.8</v>
@@ -5835,13 +5902,13 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
@@ -5853,7 +5920,7 @@
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5907,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" t="n">
-        <v>0.229</v>
+        <v>0.232</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,34 +6033,34 @@
         <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O31" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="P31" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S31" t="n">
         <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U31" t="n">
         <v>20.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
         <v>7.6</v>
@@ -6008,16 +6075,16 @@
         <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,10 +6096,10 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6053,13 +6120,13 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>30</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6083,10 +6150,10 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-20-2008-09</t>
+          <t>2009-03-20</t>
         </is>
       </c>
     </row>
